--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_120_Cameroon.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_120_Cameroon.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R353c6ca2403b4336"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R61f2aaf9f1af4077"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R347baacd3fb04498"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re9d0f18484614a55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R29642d94f33342e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf78ef1d364814d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R793fd8de94f048e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R574e4f05c3364c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R900a202c71894da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rcce04f587de04f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3e45b39a5b9447b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3b9556f8f40a4a14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ120CommercialTable" displayName="EEZ120CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ120CommercialTable" displayName="EEZ120CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ120FunctionalTable" displayName="EEZ120FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ120FunctionalTable" displayName="EEZ120FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ120ValidationTable" displayName="EEZ120ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ120ValidationTable" displayName="EEZ120ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4915,7 +4869,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fd66aefea344078"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fde6d2be1bc490a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4925,20 +4879,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4946,498 +4890,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1263.2975894018</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.324739632748912</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>211.22223453814414</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1263.2975894018</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>264.3117455674025</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$64,A2,'Species'!$U$2:$U$64))</x:f>
-        <x:v>333904.39102588146</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.324739632748912</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>211.22223453814414</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>266836.5397200991</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>67067.85130578233</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.251344330038659</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.25134433003865897</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>72.1580872775</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.36</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>229.08676527677724</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>72.1580872775</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>229.08676527677727</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$64,A3,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>16530.46280296185</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.36</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>16530.46280296185</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>104544.0000000002</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.5173948767982863</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>32.9150771061581</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>104544.0000000002</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>35.12880717486664</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$64,A4,'Species'!$U$2:$U$64))</x:f>
-        <x:v>3672506.0172892646</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.5173948767982863</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>32.9150771061581</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3441073.820986199</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>231432.1963030654</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0672558068622713</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0672558068622712</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
+        <x:v>1853.0583000202</x:v>
+      </x:c>
+      <x:c r="C5" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
-        <x:v>1853.0583000202</x:v>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1853.0583000202</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$64,A5,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>18530.583000202</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>18530.583000202</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>80885.74663630538</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.2875612735681523</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>193.89261751048463</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>80885.74663630538</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>203.3117932744453</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$64,A6,'Species'!$U$2:$U$64))</x:f>
-        <x:v>16445026.19896968</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.2875612735681523</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>193.89261751048463</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>15683149.134603128</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>761877.064366553</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.048579341931115</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.04857934193111483</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>86405.6483346829</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.8001965438137373</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>631.2429544367465</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>86405.6483346829</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>872.0389000058069</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$64,A7,'Species'!$U$2:$U$64))</x:f>
-        <x:v>75349086.52806546</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.8001965438137373</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>631.2429544367465</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>54542956.73480778</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>20806129.793257676</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.38146318129431</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.3814631812943098</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4198.509545645599</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.460716450475769</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>288.8793182386671</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4198.509545645599</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>320.96297544620114</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$64,A8,'Species'!$U$2:$U$64))</x:f>
-        <x:v>1347566.1162096895</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.460716450475769</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>288.8793182386671</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1212862.5751646368</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>134703.5410450527</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.111062492819327</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.11106249281932681</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1287.4998010243</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.485731074414817</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>3060.067979228066</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1287.4998010243</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>3060.420699679489</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$64,A9,'Species'!$U$2:$U$64))</x:f>
-        <x:v>3940291.0418879916</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.485731074414817</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>3060.067979228066</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3939836.914376967</x:v>
       </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>454.1275110244751</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0001152655607057</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.00011526556070564899</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4984b05356c34540"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reaf7bb688e5b4832"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5447,20 +5067,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5468,1092 +5078,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>617.8560182639999</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.269873433295641</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1861.544546546375</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>617.8560182639999</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1861.7524412189696</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$64,A2,'Species'!$U$2:$U$64))</x:f>
-        <x:v>1150294.950324834</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.269873433295641</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1861.544546546375</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1150166.5013502063</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>128.44897462776862</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.000111678591297</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00011167859129698133</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>617.6860182639999</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.14</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>13.803842646028853</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>617.6860182639999</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>13.803842646028853</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$64,A3,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>8526.44060076836</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.14</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>13.803842646028853</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>8526.44060076836</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>24538.74196826</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.7907172451545614</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>617.6141609544775</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>24538.74196826</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>617.9209207842008</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$64,A4,'Species'!$U$2:$U$64))</x:f>
-        <x:v>15163002.031913131</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.7907172451545614</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>617.6141609544775</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>15155474.531605324</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>7527.500307807699</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0004966852269859</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0004966852269857867</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>10436.1657559034</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.410016000929724</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2570.490486896289</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>10436.1657559034</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2575.9112741873587</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$64,A5,'Species'!$U$2:$U$64))</x:f>
-        <x:v>26882637.029919606</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.410016000929724</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2570.490486896289</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>26826064.795222506</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>56572.234697099775</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0021088532786655</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0021088532786655615</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3447.0986096885</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.38</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>239.88329190194898</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3447.0986096885</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$64,A6,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>826901.362002709</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.38</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>826901.362002709</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>796.6861408781</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.288800141779113</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1944.465051235116</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>796.6861408781</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2533.351532729999</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$64,A7,'Species'!$U$2:$U$64))</x:f>
-        <x:v>2018286.0560982823</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.288800141779113</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1944.465051235116</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1549128.3577408416</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>469157.69835744076</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3028526952031483</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.3028526952031483</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>91.37126311120001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.054961942277281</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1134.9113577328128</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>91.37126311120001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1140.48850183601</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$64,A8,'Species'!$U$2:$U$64))</x:f>
-        <x:v>104207.8749765564</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.054961942277281</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1134.9113577328128</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>103698.28427529408</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>509.5907012623211</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0049141671419508</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.004914167141950777</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1235.0618228299</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.3250766076451974</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>211.3861882933061</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1235.0618228299</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>265.68660884792547</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$64,A9,'Species'!$U$2:$U$64))</x:f>
-        <x:v>328139.38742521347</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.3250766076451974</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>211.3861882933061</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>261075.01103459508</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>67064.37639061839</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.256877807358329</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.2568778073583292</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5282.0988352879</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.4741860290040587</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>297.97925431184905</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5282.0988352879</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>537.1532007938748</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$64,A10,'Species'!$U$2:$U$64))</x:f>
-        <x:v>2837296.296284494</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.4741860290040587</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>297.97925431184905</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1573955.872140575</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1263340.424143919</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.8026530136615457</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.8026530136615457</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>101939.6058072988</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.396635331997545</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>249.25009470465784</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>101939.6058072988</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>328.9198536450019</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$64,A11,'Species'!$U$2:$U$64))</x:f>
-        <x:v>33529960.222765908</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.396635331997545</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>249.25009470465784</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>25408456.401624713</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>8121503.821141195</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.319637828161095</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.31963782816109504</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>105043.71940789229</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.5495808539689118</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>35.44711171404788</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>105043.71940789229</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>57.52326381093497</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$64,A12,'Species'!$U$2:$U$64))</x:f>
-        <x:v>6042457.583182018</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.5495808539689118</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>35.44711171404788</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>3723496.456710657</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>2318961.126471361</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.6227912805696438</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.6227912805696437</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>10178.657957130601</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.683603161678241</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>482.6176067279255</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>10178.657957130601</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>667.7723935094364</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$64,A13,'Species'!$U$2:$U$64))</x:f>
-        <x:v>6797026.786746971</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.683603161678241</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>482.6176067279255</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>4912399.542972526</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1884627.2437744457</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.3836469788925283</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.3836469788925282</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
+      <x:c r="B14" s="31" t="n">
+        <x:v>1853.0583000202</x:v>
+      </x:c>
+      <x:c r="C14" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
-        <x:v>1853.0583000202</x:v>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1853.0583000202</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$64,A14,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>18530.583000202</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>18530.583000202</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>28.2357665719</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>28.2357665719</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$64,A15,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>5765.003600667972</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>5765.003600667972</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>10275.9908598961</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.61802409157586</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>414.9770619783718</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>10275.9908598961</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>457.7360892269386</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$64,A16,'Species'!$U$2:$U$64))</x:f>
-        <x:v>4703691.869140606</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.61802409157586</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>414.9770619783718</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>4264300.495956286</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>439391.3731843205</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1030394958331344</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.10303949583313436</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>2778.0000000003</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.8060583153347696</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>63.982074229803686</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>2778.0000000003</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>69.89098185695744</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$64,A17,'Species'!$U$2:$U$64))</x:f>
-        <x:v>194157.14759864873</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.8060583153347696</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>63.982074229803686</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>177742.20221041385</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>16414.94538823489</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0923525487143602</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0923525487143601</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>617.6860029373</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>617.6860029373</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$64,A18,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>79573.37163711005</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>79573.37163711005</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>72.1580872775</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.36</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>229.08676527677724</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>72.1580872775</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>229.08676527677727</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$64,A19,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>16530.46280296185</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.36</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>16530.46280296185</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>660.0396728459</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>630.957344480193</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>660.0396728459</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>630.9573444801929</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$64,A20,'Species'!$U$2:$U$64))</x:f>
-        <x:v>416456.87923042435</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>416456.8792304244</x:v>
       </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>-5.820766091346741e-11</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>0.9999999999999999</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>-1.397687583430727e-16</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b606fef0ee542e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f85c1ae7cea4e89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6728,7 +5629,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6827,7 +5728,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>101123441.33925112</x:v>
+        <x:v>79121776.76546197</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6841,7 +5742,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>101123441.3392511</x:v>
+        <x:v>86478242.55571876</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6855,7 +5756,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-22001664.57378915</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6869,7 +5770,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.4901161193847656e-8</x:v>
+        <x:v>-14645198.783532351</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6880,9 +5781,9 @@
         <x:v>EEZ_120</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6894,47 +5795,19 @@
         <x:v>EEZ_120</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_120</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_120</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4640505853a44e9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a9abc8272d643f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6981,7 +5854,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
